--- a/main/ig/StructureDefinition-FRLMPregnancyHistory.xlsx
+++ b/main/ig/StructureDefinition-FRLMPregnancyHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T14:19:44+00:00</t>
+    <t>2026-09-14T09:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMPregnancyHistory.xlsx
+++ b/main/ig/StructureDefinition-FRLMPregnancyHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:04:12+00:00</t>
+    <t>2026-09-23T09:36:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMPregnancyHistory.xlsx
+++ b/main/ig/StructureDefinition-FRLMPregnancyHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:36:17+00:00</t>
+    <t>2026-09-28T10:07:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMPregnancyHistory.xlsx
+++ b/main/ig/StructureDefinition-FRLMPregnancyHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:07:47+00:00</t>
+    <t>2026-09-30T20:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -283,7 +283,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l’entrée</t>
+    <t>Identifiant</t>
   </si>
   <si>
     <t>FRLMEntry.header.identifier</t>
@@ -477,7 +477,7 @@
     <t>jdv-historique-grossesses-cisis (1.2.250.1.213.1.1.5.852)</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-historique-grossesses-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-historique-grossesses-cisis|20260916095454</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.method</t>

--- a/main/ig/StructureDefinition-FRLMPregnancyHistory.xlsx
+++ b/main/ig/StructureDefinition-FRLMPregnancyHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:10:21+00:00</t>
+    <t>2026-10-08T12:56:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
